--- a/artfynd/A 42583-2025 artfynd.xlsx
+++ b/artfynd/A 42583-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515658</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515657</v>
       </c>
       <c r="B3" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515648</v>
       </c>
       <c r="B4" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128515651</v>
       </c>
       <c r="B5" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42583-2025 artfynd.xlsx
+++ b/artfynd/A 42583-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515658</v>
       </c>
       <c r="B2" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515657</v>
       </c>
       <c r="B3" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515648</v>
       </c>
       <c r="B4" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128515651</v>
       </c>
       <c r="B5" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42583-2025 artfynd.xlsx
+++ b/artfynd/A 42583-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515658</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515657</v>
       </c>
       <c r="B3" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515648</v>
       </c>
       <c r="B4" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128515651</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42583-2025 artfynd.xlsx
+++ b/artfynd/A 42583-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515658</v>
       </c>
       <c r="B2" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515657</v>
       </c>
       <c r="B3" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515648</v>
       </c>
       <c r="B4" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128515651</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42583-2025 artfynd.xlsx
+++ b/artfynd/A 42583-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515658</v>
       </c>
       <c r="B2" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515657</v>
       </c>
       <c r="B3" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515648</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128515651</v>
       </c>
       <c r="B5" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42583-2025 artfynd.xlsx
+++ b/artfynd/A 42583-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515658</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515657</v>
       </c>
       <c r="B3" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515648</v>
       </c>
       <c r="B4" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128515651</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42583-2025 artfynd.xlsx
+++ b/artfynd/A 42583-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515658</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515657</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515648</v>
       </c>
       <c r="B4" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128515651</v>
       </c>
       <c r="B5" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42583-2025 artfynd.xlsx
+++ b/artfynd/A 42583-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515658</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515657</v>
       </c>
       <c r="B3" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515648</v>
       </c>
       <c r="B4" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128515651</v>
       </c>
       <c r="B5" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42583-2025 artfynd.xlsx
+++ b/artfynd/A 42583-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515658</v>
       </c>
       <c r="B2" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515657</v>
       </c>
       <c r="B3" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515648</v>
       </c>
       <c r="B4" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128515651</v>
       </c>
       <c r="B5" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42583-2025 artfynd.xlsx
+++ b/artfynd/A 42583-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515658</v>
       </c>
       <c r="B2" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515657</v>
       </c>
       <c r="B3" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515648</v>
       </c>
       <c r="B4" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128515651</v>
       </c>
       <c r="B5" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42583-2025 artfynd.xlsx
+++ b/artfynd/A 42583-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128515658</v>
+        <v>128515648</v>
       </c>
       <c r="B2" t="n">
-        <v>92811</v>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632406</v>
+        <v>632370</v>
       </c>
       <c r="R2" t="n">
-        <v>6642312</v>
+        <v>6642348</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128515657</v>
+        <v>128515658</v>
       </c>
       <c r="B3" t="n">
-        <v>92847</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632407</v>
+        <v>632406</v>
       </c>
       <c r="R3" t="n">
         <v>6642312</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128515648</v>
+        <v>128515650</v>
       </c>
       <c r="B4" t="n">
-        <v>92218</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632370</v>
+        <v>632425</v>
       </c>
       <c r="R4" t="n">
-        <v>6642348</v>
+        <v>6642279</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -969,7 +969,7 @@
         <v>128515651</v>
       </c>
       <c r="B5" t="n">
-        <v>92456</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,6 +1060,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128515657</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Östra Fibysjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>632407</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6642312</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
